--- a/docs/source/07_Manual_Medel_Name.xlsx
+++ b/docs/source/07_Manual_Medel_Name.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F00A17A-B7BB-49DB-8697-FD57E5B8ABEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CFB9F96-28D6-4AFD-A662-7A626FDAAF2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18012" yWindow="2592" windowWidth="12360" windowHeight="15888" xr2:uid="{98EA4B3B-0244-4AA2-B2C9-7F907D568B40}"/>
+    <workbookView xWindow="18084" yWindow="2352" windowWidth="12204" windowHeight="15888" xr2:uid="{98EA4B3B-0244-4AA2-B2C9-7F907D568B40}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="50">
   <si>
     <t>model</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -137,6 +137,90 @@
   </si>
   <si>
     <t>253035LE-7 OM, 253035LE-7 SM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22B-9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25B-9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30B-9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>32B-9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>35B-9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2225303235B-9_OM, 2225303235B-9_SM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25B-9U</t>
+  </si>
+  <si>
+    <t>30B-9U</t>
+  </si>
+  <si>
+    <t>32B-9U</t>
+  </si>
+  <si>
+    <t>35B-9U</t>
+  </si>
+  <si>
+    <t>25/30/32/35B-9U</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22/25/30/32/35B-9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25303235B-9U_OM, 25303235B-9U_SM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15BCS-9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18BCS-9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20BCS-9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15/18/20BCS-9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15BCS-9U</t>
+  </si>
+  <si>
+    <t>15/18/20BCS-9U</t>
+  </si>
+  <si>
+    <t>18BCS-9U</t>
+  </si>
+  <si>
+    <t>20BCS-9U</t>
+  </si>
+  <si>
+    <t>151820BCS-9_OM, 151820BCS-9_SM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>151820BCS-9U OM ENG, 151820BCS-9U SM ENG</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -539,12 +623,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA36ACF8-6D28-4DDB-ACD4-15A67F63FC2E}">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.19921875" customWidth="1"/>
     <col min="2" max="2" width="19.8984375" customWidth="1"/>
-    <col min="3" max="3" width="38.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
@@ -724,34 +808,214 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
+      <c r="A17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
+      <c r="A18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
+      <c r="A19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
+      <c r="A20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
+      <c r="A21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
+      <c r="A22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A26" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A27" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A29" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A30" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A31" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
